--- a/outputs/holdout_70_30/metrics_holdout.xlsx
+++ b/outputs/holdout_70_30/metrics_holdout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -486,13 +486,13 @@
         <v>141</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5555991730175903</v>
+        <v>0.1440574800187847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009997578336502744</v>
+        <v>0.01393688030564516</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006995782633244294</v>
+        <v>0.007712419711980546</v>
       </c>
       <c r="H2" t="n">
         <v>0.3</v>
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -522,13 +522,13 @@
         <v>141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1165990968717192</v>
+        <v>0.5555991730175903</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01408791743410722</v>
+        <v>0.009997578336502744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01207517479498072</v>
+        <v>0.006995782633244294</v>
       </c>
       <c r="H3" t="n">
         <v>0.3</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -558,13 +558,13 @@
         <v>141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8404519752383224</v>
+        <v>0.1165990968717192</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005990362478772076</v>
+        <v>0.01408791743410722</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002436032224103462</v>
+        <v>0.01207517479498072</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -579,28 +579,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>('corn', 'alkaline')</t>
+          <t>('corn', 'acid')</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>281</v>
+        <v>796</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5358020113055064</v>
+        <v>0.8404519752383224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01819113763779448</v>
+        <v>0.005990362478772076</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01216493487087482</v>
+        <v>0.002436032224103462</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -620,7 +620,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -630,13 +630,13 @@
         <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5050197446801864</v>
+        <v>-0.2838319980450943</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01899392638488519</v>
+        <v>0.03062871650869186</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01539351442070242</v>
+        <v>0.01363268178670587</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -656,7 +656,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -666,13 +666,13 @@
         <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8308706374027023</v>
+        <v>0.5358020113055064</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01090479739268936</v>
+        <v>0.01819113763779448</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003442783347925349</v>
+        <v>0.01216493487087483</v>
       </c>
       <c r="H7" t="n">
         <v>0.3</v>
@@ -687,28 +687,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4521908359420388</v>
+        <v>0.5050197446801864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006894118789865913</v>
+        <v>0.01899392638488519</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004693613323836235</v>
+        <v>0.01539351442070242</v>
       </c>
       <c r="H8" t="n">
         <v>0.3</v>
@@ -723,28 +723,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.445823408001962</v>
+        <v>0.8308706374027023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0145672195019129</v>
+        <v>0.01090479739268936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01351024713157459</v>
+        <v>0.003442783347925349</v>
       </c>
       <c r="H9" t="n">
         <v>0.3</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -774,13 +774,13 @@
         <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>0.71854871160829</v>
+        <v>-41.58898209764424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004941578926517523</v>
+        <v>0.06579550100604518</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001757530290196386</v>
+        <v>0.03022101544513479</v>
       </c>
       <c r="H10" t="n">
         <v>0.3</v>
@@ -795,7 +795,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1084</v>
+        <v>296</v>
       </c>
       <c r="D11" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5403752182019719</v>
+        <v>0.4521908359420388</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01280507360501254</v>
+        <v>0.006894118789865913</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00921577581198311</v>
+        <v>0.004693613323836235</v>
       </c>
       <c r="H11" t="n">
         <v>0.3</v>
@@ -831,7 +831,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1084</v>
+        <v>296</v>
       </c>
       <c r="D12" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2455103031313047</v>
+        <v>-1.445823408001962</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01651302341198076</v>
+        <v>0.0145672195019129</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01427394997885205</v>
+        <v>0.01351024713157459</v>
       </c>
       <c r="H12" t="n">
         <v>0.3</v>
@@ -867,7 +867,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1084</v>
+        <v>296</v>
       </c>
       <c r="D13" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8047020549621022</v>
+        <v>0.71854871160829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008346976631316233</v>
+        <v>0.004941578926517523</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004111520514605777</v>
+        <v>0.001757530290196386</v>
       </c>
       <c r="H13" t="n">
         <v>0.3</v>
@@ -903,28 +903,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>405</v>
+        <v>1084</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5726161403301757</v>
+        <v>-0.2369837375451027</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01810193382314534</v>
+        <v>0.0212582738829628</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01306317615897631</v>
+        <v>0.01382151771771696</v>
       </c>
       <c r="H14" t="n">
         <v>0.3</v>
@@ -939,28 +939,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>405</v>
+        <v>1084</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5362965362576724</v>
+        <v>0.540375218201972</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01885541452046828</v>
+        <v>0.01280507360501254</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01593411864050258</v>
+        <v>0.00921577581198311</v>
       </c>
       <c r="H15" t="n">
         <v>0.3</v>
@@ -975,28 +975,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>405</v>
+        <v>1084</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8577563926749527</v>
+        <v>0.2455103031313047</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01044316868895962</v>
+        <v>0.01651302341198076</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003442961621520507</v>
+        <v>0.01427394997885205</v>
       </c>
       <c r="H16" t="n">
         <v>0.3</v>
@@ -1011,28 +1011,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>1084</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4015658603662042</v>
+        <v>0.8047020549621022</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03404891297029863</v>
+        <v>0.008346976631316233</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02107890552241906</v>
+        <v>0.004111520514605777</v>
       </c>
       <c r="H17" t="n">
         <v>0.3</v>
@@ -1047,28 +1047,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85</v>
+        <v>405</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6119596572930717</v>
+        <v>-0.8149627419761496</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02563939410459317</v>
+        <v>0.03754497355592332</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01860713135330304</v>
+        <v>0.02006681720547799</v>
       </c>
       <c r="H18" t="n">
         <v>0.3</v>
@@ -1083,28 +1083,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85</v>
+        <v>405</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5625892695902999</v>
+        <v>0.5726161403301757</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02910983790532751</v>
+        <v>0.01810193382314534</v>
       </c>
       <c r="G19" t="n">
-        <v>0.008968077334825016</v>
+        <v>0.01306317615897632</v>
       </c>
       <c r="H19" t="n">
         <v>0.3</v>
@@ -1119,28 +1119,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>134</v>
+        <v>405</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4461528411019057</v>
+        <v>0.5362965362576724</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01720765894067686</v>
+        <v>0.01885541452046828</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01118684718818989</v>
+        <v>0.01593411864050258</v>
       </c>
       <c r="H20" t="n">
         <v>0.3</v>
@@ -1155,28 +1155,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>134</v>
+        <v>405</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4091125617233837</v>
+        <v>0.8577563926749527</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01777375552529767</v>
+        <v>0.01044316868895962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01453549335444625</v>
+        <v>0.003442961621520507</v>
       </c>
       <c r="H21" t="n">
         <v>0.3</v>
@@ -1191,28 +1191,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7440258050863866</v>
+        <v>-5.081594923066781</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01169835823295638</v>
+        <v>0.119084443313332</v>
       </c>
       <c r="G22" t="n">
-        <v>0.003606943049791915</v>
+        <v>0.08114870114764144</v>
       </c>
       <c r="H22" t="n">
         <v>0.3</v>
@@ -1227,7 +1227,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1236,19 +1236,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>878</v>
+        <v>85</v>
       </c>
       <c r="D23" t="n">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5923956541798592</v>
+        <v>0.4015658603662041</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0293385282557128</v>
+        <v>0.03404891297029863</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0209796044758084</v>
+        <v>0.02107890552241907</v>
       </c>
       <c r="H23" t="n">
         <v>0.3</v>
@@ -1263,7 +1263,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>878</v>
+        <v>85</v>
       </c>
       <c r="D24" t="n">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.696338925785533</v>
+        <v>0.6119596572930717</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02528040625088436</v>
+        <v>0.02563939410459317</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01995855149482977</v>
+        <v>0.01860713135330304</v>
       </c>
       <c r="H24" t="n">
         <v>0.3</v>
@@ -1299,36 +1299,324 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>('potato', 'alkaline')</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>85</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5625892695902999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02910983790532751</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.008968077334825016</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>42</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>134</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-26.00942176287718</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1297200934968934</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.100413513420541</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>42</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>134</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4461528411019057</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.01720765894067686</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01118684718818989</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>134</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.4091125617233837</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.01777375552529767</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.01453549335444625</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>134</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7440258050863866</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.01169835823295638</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.003606943049791915</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>42</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>('potato', 'strong_acid')</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>878</v>
+      </c>
+      <c r="D30" t="n">
+        <v>156</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1810049273417552</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.04136466586033474</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.02708435917761802</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>42</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>878</v>
+      </c>
+      <c r="D31" t="n">
+        <v>156</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5923956541798592</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0293385282557128</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0209796044758084</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>42</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>878</v>
+      </c>
+      <c r="D32" t="n">
+        <v>156</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.696338925785533</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.02528040625088436</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.01995855149482977</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>42</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>xgb</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C33" t="n">
         <v>878</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D33" t="n">
         <v>156</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E33" t="n">
         <v>0.8553292149041127</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F33" t="n">
         <v>0.01747870853113931</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G33" t="n">
         <v>0.007702735048469942</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I25" t="n">
-        <v>42</v>
-      </c>
-      <c r="J25" t="b">
+      <c r="H33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>42</v>
+      </c>
+      <c r="J33" t="b">
         <v>1</v>
       </c>
     </row>

--- a/outputs/holdout_70_30/metrics_holdout.xlsx
+++ b/outputs/holdout_70_30/metrics_holdout.xlsx
@@ -954,7 +954,7 @@
         <v>192</v>
       </c>
       <c r="E15" t="n">
-        <v>0.540375218201972</v>
+        <v>0.5403752182019719</v>
       </c>
       <c r="F15" t="n">
         <v>0.01280507360501254</v>
@@ -1104,7 +1104,7 @@
         <v>0.01810193382314534</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01306317615897632</v>
+        <v>0.01306317615897631</v>
       </c>
       <c r="H19" t="n">
         <v>0.3</v>
@@ -1242,7 +1242,7 @@
         <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4015658603662041</v>
+        <v>0.4015658603662042</v>
       </c>
       <c r="F23" t="n">
         <v>0.03404891297029863</v>

--- a/outputs/holdout_70_30/metrics_holdout.xlsx
+++ b/outputs/holdout_70_30/metrics_holdout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,16 @@
           <t>split_by_group</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mix_train_into_test</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mix_fraction</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>796</v>
+        <v>714</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1440574800187847</v>
+        <v>0.621144429828969</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01393688030564516</v>
+        <v>0.03082173243440424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007712419711980546</v>
+        <v>0.01144714611236995</v>
       </c>
       <c r="H2" t="n">
         <v>0.3</v>
@@ -501,6 +511,12 @@
         <v>42</v>
       </c>
       <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -512,23 +528,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>796</v>
+        <v>714</v>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5555991730175903</v>
+        <v>0.6336224600100473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009997578336502744</v>
+        <v>0.03047354088498036</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006995782633244294</v>
+        <v>0.01005657375651105</v>
       </c>
       <c r="H3" t="n">
         <v>0.3</v>
@@ -537,6 +553,12 @@
         <v>42</v>
       </c>
       <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -548,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>796</v>
+        <v>714</v>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1165990968717192</v>
+        <v>0.3076572508189097</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01408791743410722</v>
+        <v>0.04166590138756862</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01207517479498072</v>
+        <v>0.01734550778493212</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -573,6 +595,12 @@
         <v>42</v>
       </c>
       <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -584,23 +612,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>796</v>
+        <v>714</v>
       </c>
       <c r="D5" t="n">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8404519752383224</v>
+        <v>0.5039561330180508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005990362478772076</v>
+        <v>0.03679037296224915</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002436032224103462</v>
+        <v>0.02316472206685717</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -609,34 +637,40 @@
         <v>42</v>
       </c>
       <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>('corn', 'alkaline')</t>
+          <t>('corn', 'acid')</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>281</v>
+        <v>714</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>306</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2838319980450943</v>
+        <v>0.4645808794240086</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03062871650869186</v>
+        <v>0.0366114541255777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01363268178670587</v>
+        <v>0.01058609120153027</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -645,6 +679,12 @@
         <v>42</v>
       </c>
       <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -656,23 +696,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5358020113055064</v>
+        <v>0.7731692220392055</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01819113763779448</v>
+        <v>0.04317907745051617</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01216493487087483</v>
+        <v>0.01677927773926535</v>
       </c>
       <c r="H7" t="n">
         <v>0.3</v>
@@ -681,6 +721,12 @@
         <v>42</v>
       </c>
       <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -692,23 +738,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5050197446801864</v>
+        <v>0.6771275098923033</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01899392638488519</v>
+        <v>0.05281041965184029</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01539351442070242</v>
+        <v>0.0223169610595146</v>
       </c>
       <c r="H8" t="n">
         <v>0.3</v>
@@ -717,6 +763,12 @@
         <v>42</v>
       </c>
       <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -728,23 +780,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8308706374027023</v>
+        <v>0.4669512213449573</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01090479739268936</v>
+        <v>0.0661920519304825</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003442783347925349</v>
+        <v>0.03746757003676752</v>
       </c>
       <c r="H9" t="n">
         <v>0.3</v>
@@ -753,34 +805,40 @@
         <v>42</v>
       </c>
       <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>-41.58898209764424</v>
+        <v>0.6222462551978036</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06579550100604518</v>
+        <v>0.05936704052289277</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03022101544513479</v>
+        <v>0.03412778738365982</v>
       </c>
       <c r="H10" t="n">
         <v>0.3</v>
@@ -789,34 +847,40 @@
         <v>42</v>
       </c>
       <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4521908359420388</v>
+        <v>0.7701204251402211</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006894118789865913</v>
+        <v>0.04355728606101761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004693613323836235</v>
+        <v>0.01593847837280477</v>
       </c>
       <c r="H11" t="n">
         <v>0.3</v>
@@ -825,6 +889,12 @@
         <v>42</v>
       </c>
       <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -836,23 +906,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.445823408001962</v>
+        <v>0.5920798401817757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0145672195019129</v>
+        <v>0.02085521015321325</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01351024713157459</v>
+        <v>0.005800123533386826</v>
       </c>
       <c r="H12" t="n">
         <v>0.3</v>
@@ -861,6 +931,12 @@
         <v>42</v>
       </c>
       <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -872,23 +948,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="E13" t="n">
-        <v>0.71854871160829</v>
+        <v>0.63469624355211</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004941578926517523</v>
+        <v>0.01798267851375202</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001757530290196386</v>
+        <v>0.006657597753971772</v>
       </c>
       <c r="H13" t="n">
         <v>0.3</v>
@@ -897,34 +973,40 @@
         <v>42</v>
       </c>
       <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1084</v>
+        <v>268</v>
       </c>
       <c r="D14" t="n">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2369837375451027</v>
+        <v>0.2922090870398967</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0212582738829628</v>
+        <v>0.02747131680045649</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01382151771771696</v>
+        <v>0.01212811780549789</v>
       </c>
       <c r="H14" t="n">
         <v>0.3</v>
@@ -933,34 +1015,40 @@
         <v>42</v>
       </c>
       <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1084</v>
+        <v>268</v>
       </c>
       <c r="D15" t="n">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5403752182019719</v>
+        <v>0.400265998230666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01280507360501254</v>
+        <v>0.02802693438256564</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00921577581198311</v>
+        <v>0.01750495870010843</v>
       </c>
       <c r="H15" t="n">
         <v>0.3</v>
@@ -969,34 +1057,40 @@
         <v>42</v>
       </c>
       <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1084</v>
+        <v>268</v>
       </c>
       <c r="D16" t="n">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2455103031313047</v>
+        <v>0.5699546681020234</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01651302341198076</v>
+        <v>0.0214206058600407</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01427394997885205</v>
+        <v>0.005674196547451998</v>
       </c>
       <c r="H16" t="n">
         <v>0.3</v>
@@ -1005,6 +1099,12 @@
         <v>42</v>
       </c>
       <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1016,23 +1116,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1084</v>
+        <v>965</v>
       </c>
       <c r="D17" t="n">
-        <v>192</v>
+        <v>414</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8047020549621022</v>
+        <v>0.595553670526872</v>
       </c>
       <c r="F17" t="n">
-        <v>0.008346976631316233</v>
+        <v>0.02686377934215209</v>
       </c>
       <c r="G17" t="n">
-        <v>0.004111520514605777</v>
+        <v>0.01347980458226976</v>
       </c>
       <c r="H17" t="n">
         <v>0.3</v>
@@ -1041,34 +1141,40 @@
         <v>42</v>
       </c>
       <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>405</v>
+        <v>965</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>414</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8149627419761496</v>
+        <v>0.6126421018285144</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03754497355592332</v>
+        <v>0.02633928510051866</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02006681720547799</v>
+        <v>0.00927770024999462</v>
       </c>
       <c r="H18" t="n">
         <v>0.3</v>
@@ -1077,13 +1183,19 @@
         <v>42</v>
       </c>
       <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1092,19 +1204,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>405</v>
+        <v>965</v>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>414</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5726161403301757</v>
+        <v>0.3315916132049433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01810193382314534</v>
+        <v>0.03453485267211293</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01306317615897631</v>
+        <v>0.01725578507660283</v>
       </c>
       <c r="H19" t="n">
         <v>0.3</v>
@@ -1113,13 +1225,19 @@
         <v>42</v>
       </c>
       <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1128,19 +1246,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>405</v>
+        <v>965</v>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>414</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5362965362576724</v>
+        <v>0.3872708699894764</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01885541452046828</v>
+        <v>0.03502473336435648</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01593411864050258</v>
+        <v>0.02266933956028253</v>
       </c>
       <c r="H20" t="n">
         <v>0.3</v>
@@ -1149,13 +1267,19 @@
         <v>42</v>
       </c>
       <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1164,19 +1288,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>405</v>
+        <v>965</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>414</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8577563926749527</v>
+        <v>0.6339514530180599</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01044316868895962</v>
+        <v>0.02557655326368751</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003442961621520507</v>
+        <v>0.00992337908428865</v>
       </c>
       <c r="H21" t="n">
         <v>0.3</v>
@@ -1185,34 +1309,40 @@
         <v>42</v>
       </c>
       <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.081594923066781</v>
+        <v>0.5837111551844303</v>
       </c>
       <c r="F22" t="n">
-        <v>0.119084443313332</v>
+        <v>0.05060103520682857</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08114870114764144</v>
+        <v>0.0143738737258207</v>
       </c>
       <c r="H22" t="n">
         <v>0.3</v>
@@ -1221,34 +1351,40 @@
         <v>42</v>
       </c>
       <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4015658603662042</v>
+        <v>0.5632243434287103</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03404891297029863</v>
+        <v>0.05214609539295193</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02107890552241907</v>
+        <v>0.01582658139581788</v>
       </c>
       <c r="H23" t="n">
         <v>0.3</v>
@@ -1257,34 +1393,40 @@
         <v>42</v>
       </c>
       <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6119596572930717</v>
+        <v>0.3219662079712442</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02563939410459317</v>
+        <v>0.06457846005672484</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01860713135330304</v>
+        <v>0.02836620729368601</v>
       </c>
       <c r="H24" t="n">
         <v>0.3</v>
@@ -1293,34 +1435,40 @@
         <v>42</v>
       </c>
       <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5625892695902999</v>
+        <v>0.5395547433842051</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02910983790532751</v>
+        <v>0.0544083179851434</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008968077334825016</v>
+        <v>0.02667314513783826</v>
       </c>
       <c r="H25" t="n">
         <v>0.3</v>
@@ -1329,34 +1477,40 @@
         <v>42</v>
       </c>
       <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>134</v>
+        <v>350</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="E26" t="n">
-        <v>-26.00942176287718</v>
+        <v>0.5394908626660671</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1297200934968934</v>
+        <v>0.05322076845489412</v>
       </c>
       <c r="G26" t="n">
-        <v>0.100413513420541</v>
+        <v>0.01403272447867107</v>
       </c>
       <c r="H26" t="n">
         <v>0.3</v>
@@ -1365,34 +1519,40 @@
         <v>42</v>
       </c>
       <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4461528411019057</v>
+        <v>0.7851859441546819</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01720765894067686</v>
+        <v>0.1007888943191273</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01118684718818989</v>
+        <v>0.03217525055954765</v>
       </c>
       <c r="H27" t="n">
         <v>0.3</v>
@@ -1401,34 +1561,40 @@
         <v>42</v>
       </c>
       <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4091125617233837</v>
+        <v>0.6070879973604461</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01777375552529767</v>
+        <v>0.1459658569019076</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01453549335444625</v>
+        <v>0.08016921831030917</v>
       </c>
       <c r="H28" t="n">
         <v>0.3</v>
@@ -1437,34 +1603,40 @@
         <v>42</v>
       </c>
       <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7440258050863866</v>
+        <v>0.3485462845809374</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01169835823295638</v>
+        <v>0.1755185878436701</v>
       </c>
       <c r="G29" t="n">
-        <v>0.003606943049791915</v>
+        <v>0.09286206671891778</v>
       </c>
       <c r="H29" t="n">
         <v>0.3</v>
@@ -1473,34 +1645,40 @@
         <v>42</v>
       </c>
       <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>878</v>
+        <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1810049273417552</v>
+        <v>0.8173083913869882</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04136466586033474</v>
+        <v>0.09196192788421111</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02708435917761802</v>
+        <v>0.04260187459700614</v>
       </c>
       <c r="H30" t="n">
         <v>0.3</v>
@@ -1509,34 +1687,40 @@
         <v>42</v>
       </c>
       <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>878</v>
+        <v>80</v>
       </c>
       <c r="D31" t="n">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5923956541798592</v>
+        <v>0.6345441873265656</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0293385282557128</v>
+        <v>0.1325358114983044</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0209796044758084</v>
+        <v>0.04563389816551194</v>
       </c>
       <c r="H31" t="n">
         <v>0.3</v>
@@ -1545,34 +1729,40 @@
         <v>42</v>
       </c>
       <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'neutral')</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>878</v>
+        <v>117</v>
       </c>
       <c r="D32" t="n">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="E32" t="n">
-        <v>0.696338925785533</v>
+        <v>0.6910228543405192</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02528040625088436</v>
+        <v>0.0289301466247686</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01995855149482977</v>
+        <v>0.009506551908296971</v>
       </c>
       <c r="H32" t="n">
         <v>0.3</v>
@@ -1581,42 +1771,390 @@
         <v>42</v>
       </c>
       <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>117</v>
+      </c>
+      <c r="D33" t="n">
+        <v>51</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5220434758442591</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.03668979583945071</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.01690329013228922</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>42</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>117</v>
+      </c>
+      <c r="D34" t="n">
+        <v>51</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3272174691796385</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.04268986775650976</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.02383261339377865</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>42</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>117</v>
+      </c>
+      <c r="D35" t="n">
+        <v>51</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5866635617520117</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.03403975200092425</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.02171622284822534</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>42</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>117</v>
+      </c>
+      <c r="D36" t="n">
+        <v>51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6844309188700763</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.02930218209910892</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0102517666423393</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>42</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>('potato', 'strong_acid')</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>756</v>
+      </c>
+      <c r="D37" t="n">
+        <v>325</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6802628587621724</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.04463533389857152</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.02181279114709053</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>42</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>756</v>
+      </c>
+      <c r="D38" t="n">
+        <v>325</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6729638333485488</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.04510387605311814</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.01745636319387993</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>42</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>756</v>
+      </c>
+      <c r="D39" t="n">
+        <v>325</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.4204235527326839</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.06009489881578905</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.03262471236514857</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>42</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>756</v>
+      </c>
+      <c r="D40" t="n">
+        <v>325</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4479053777206831</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.05904316909947419</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.03320738947300667</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>42</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>xgb</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>878</v>
-      </c>
-      <c r="D33" t="n">
-        <v>156</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.8553292149041127</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.01747870853113931</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.007702735048469942</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I33" t="n">
-        <v>42</v>
-      </c>
-      <c r="J33" t="b">
+      <c r="C41" t="n">
+        <v>756</v>
+      </c>
+      <c r="D41" t="n">
+        <v>325</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6877847944931641</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.04410717768845741</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.01730876459024492</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>42</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
     </row>
